--- a/artfynd/A 59019-2024 artfynd.xlsx
+++ b/artfynd/A 59019-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88244317</v>
+        <v>118557123</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kultsjön, Ås lm</t>
+          <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520470.8787674936</v>
+        <v>520390</v>
       </c>
       <c r="R2" t="n">
-        <v>7208657.085412485</v>
+        <v>7208253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,53 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Pettersson, Jon Andersson, Henrik Sporrong</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Elias Forsberg, Anna Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118557077</v>
+        <v>118557064</v>
       </c>
       <c r="B3" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520504</v>
+        <v>520328</v>
       </c>
       <c r="R3" t="n">
-        <v>7208434</v>
+        <v>7208227</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118557136</v>
+        <v>118557102</v>
       </c>
       <c r="B4" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520658</v>
+        <v>520591</v>
       </c>
       <c r="R4" t="n">
-        <v>7208331</v>
+        <v>7208641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118557124</v>
+        <v>118557119</v>
       </c>
       <c r="B5" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520421</v>
+        <v>520315</v>
       </c>
       <c r="R5" t="n">
-        <v>7208322</v>
+        <v>7208386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118557126</v>
+        <v>118557122</v>
       </c>
       <c r="B6" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520539</v>
+        <v>520322</v>
       </c>
       <c r="R6" t="n">
-        <v>7208282</v>
+        <v>7208235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118557117</v>
+        <v>118557049</v>
       </c>
       <c r="B7" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520464</v>
+        <v>520372</v>
       </c>
       <c r="R7" t="n">
-        <v>7208765</v>
+        <v>7208242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118557107</v>
+        <v>118557079</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1346,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520466</v>
+        <v>520482</v>
       </c>
       <c r="R8" t="n">
-        <v>7208495</v>
+        <v>7208464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118557135</v>
+        <v>118557107</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1448,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520323</v>
+        <v>520466</v>
       </c>
       <c r="R9" t="n">
-        <v>7208430</v>
+        <v>7208495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118557074</v>
+        <v>118557135</v>
       </c>
       <c r="B10" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520574</v>
+        <v>520323</v>
       </c>
       <c r="R10" t="n">
-        <v>7208654</v>
+        <v>7208430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118557062</v>
+        <v>118557137</v>
       </c>
       <c r="B11" t="n">
-        <v>90908</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520278</v>
+        <v>520694</v>
       </c>
       <c r="R11" t="n">
-        <v>7208367</v>
+        <v>7208330</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118557102</v>
+        <v>118557047</v>
       </c>
       <c r="B12" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520591</v>
+        <v>520467</v>
       </c>
       <c r="R12" t="n">
-        <v>7208641</v>
+        <v>7208753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118557109</v>
+        <v>118557124</v>
       </c>
       <c r="B13" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,39 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520438</v>
+        <v>520421</v>
       </c>
       <c r="R13" t="n">
-        <v>7208295</v>
+        <v>7208322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,55 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118557080</v>
+        <v>118557062</v>
       </c>
       <c r="B14" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520625</v>
+        <v>520278</v>
       </c>
       <c r="R14" t="n">
-        <v>7208310</v>
+        <v>7208367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118557119</v>
+        <v>118557106</v>
       </c>
       <c r="B15" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520315</v>
+        <v>520486</v>
       </c>
       <c r="R15" t="n">
-        <v>7208386</v>
+        <v>7208469</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118557122</v>
+        <v>118557063</v>
       </c>
       <c r="B16" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520322</v>
+        <v>520273</v>
       </c>
       <c r="R16" t="n">
-        <v>7208235</v>
+        <v>7208291</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118557110</v>
+        <v>118557076</v>
       </c>
       <c r="B17" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520523</v>
+        <v>520600</v>
       </c>
       <c r="R17" t="n">
-        <v>7208301</v>
+        <v>7208469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,59 +2227,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118557081</v>
+        <v>118557103</v>
       </c>
       <c r="B18" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520679</v>
+        <v>520607</v>
       </c>
       <c r="R18" t="n">
-        <v>7208301</v>
+        <v>7208559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118557079</v>
+        <v>118557125</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520482</v>
+        <v>520488</v>
       </c>
       <c r="R19" t="n">
-        <v>7208464</v>
+        <v>7208310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118557108</v>
+        <v>118557136</v>
       </c>
       <c r="B20" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2589,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520412</v>
+        <v>520658</v>
       </c>
       <c r="R20" t="n">
-        <v>7208314</v>
+        <v>7208331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118557105</v>
+        <v>88244317</v>
       </c>
       <c r="B21" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2667,34 +2529,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Kultsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520598</v>
+        <v>520471</v>
       </c>
       <c r="R21" t="n">
-        <v>7208450</v>
+        <v>7208657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,12 +2588,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2741,62 +2608,66 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Julia Pettersson, Jon Andersson, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118557106</v>
+        <v>118557048</v>
       </c>
       <c r="B22" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520486</v>
+        <v>520310</v>
       </c>
       <c r="R22" t="n">
-        <v>7208469</v>
+        <v>7208403</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,15 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118557103</v>
+        <v>118557075</v>
       </c>
       <c r="B23" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,34 +2737,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520607</v>
+        <v>520591</v>
       </c>
       <c r="R23" t="n">
-        <v>7208559</v>
+        <v>7208616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2957,15 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118557125</v>
+        <v>118557080</v>
       </c>
       <c r="B24" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,31 +2839,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520488</v>
+        <v>520625</v>
       </c>
       <c r="R24" t="n">
         <v>7208310</v>
@@ -3059,15 +2930,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118557123</v>
+        <v>118557109</v>
       </c>
       <c r="B25" t="n">
-        <v>77440</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3075,34 +2941,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520390</v>
+        <v>520438</v>
       </c>
       <c r="R25" t="n">
-        <v>7208253</v>
+        <v>7208295</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3161,15 +3032,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118557048</v>
+        <v>118557120</v>
       </c>
       <c r="B26" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3197,7 +3063,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3206,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520310</v>
+        <v>520270</v>
       </c>
       <c r="R26" t="n">
-        <v>7208403</v>
+        <v>7208346</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3268,15 +3134,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118557049</v>
+        <v>133413453</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,37 +3145,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>102954</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Marsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520372</v>
+        <v>520528</v>
       </c>
       <c r="R27" t="n">
-        <v>7208242</v>
+        <v>7208775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3338,12 +3211,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3358,27 +3241,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Erika Lorde</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elias Forsberg, Anna Johansson</t>
+          <t>Erika Lorde</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118557075</v>
+        <v>118557081</v>
       </c>
       <c r="B28" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,16 +3264,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3403,10 +3281,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3415,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520591</v>
+        <v>520679</v>
       </c>
       <c r="R28" t="n">
-        <v>7208616</v>
+        <v>7208301</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,15 +3359,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118557121</v>
+        <v>102266866</v>
       </c>
       <c r="B29" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3493,37 +3370,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>221343</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Marsliden, Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520313</v>
+        <v>520611</v>
       </c>
       <c r="R29" t="n">
-        <v>7208253</v>
+        <v>7208667</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3547,12 +3430,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3567,49 +3460,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elias Forsberg, Anna Johansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118557047</v>
+        <v>118557077</v>
       </c>
       <c r="B30" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3619,10 +3507,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520467</v>
+        <v>520504</v>
       </c>
       <c r="R30" t="n">
-        <v>7208753</v>
+        <v>7208434</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3681,37 +3569,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118557076</v>
+        <v>118557082</v>
       </c>
       <c r="B31" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3721,10 +3604,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520600</v>
+        <v>520700</v>
       </c>
       <c r="R31" t="n">
-        <v>7208469</v>
+        <v>7208335</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3783,37 +3666,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118557063</v>
+        <v>118557110</v>
       </c>
       <c r="B32" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3823,10 +3701,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520273</v>
+        <v>520523</v>
       </c>
       <c r="R32" t="n">
-        <v>7208291</v>
+        <v>7208301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3885,37 +3763,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118557064</v>
+        <v>118557118</v>
       </c>
       <c r="B33" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3925,10 +3798,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520328</v>
+        <v>520537</v>
       </c>
       <c r="R33" t="n">
-        <v>7208227</v>
+        <v>7208705</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,215 +3857,6 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>118557118</v>
-      </c>
-      <c r="B34" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>520537</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7208705</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>118557120</v>
-      </c>
-      <c r="B35" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>520270</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7208346</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59019-2024 artfynd.xlsx
+++ b/artfynd/A 59019-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3264,27 +3264,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133413453</v>
+        <v>136162944</v>
       </c>
       <c r="B27" t="n">
-        <v>57386</v>
+        <v>57820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102954</v>
+        <v>102620</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3292,19 +3292,23 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Marsliden, Ås lm</t>
@@ -3341,22 +3345,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,16 +3376,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133413453</t>
+          <t>https://artportalen.se/Sighting/136162944</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118557081</v>
+        <v>133413453</v>
       </c>
       <c r="B28" t="n">
-        <v>58057</v>
+        <v>57386</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3393,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>102954</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3418,27 +3412,30 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Marsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520679</v>
+        <v>520528</v>
       </c>
       <c r="R28" t="n">
-        <v>7208301</v>
+        <v>7208775</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3462,12 +3459,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3482,27 +3489,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Erika Lorde</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elias Forsberg, Anna Johansson</t>
+          <t>Erika Lorde</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118557081</t>
+          <t>https://artportalen.se/Sighting/133413453</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102266866</v>
+        <v>118557081</v>
       </c>
       <c r="B29" t="n">
-        <v>102464</v>
+        <v>58057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,43 +3517,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221343</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Marsliden, Vilhelmina, Ås lm</t>
+          <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520611</v>
+        <v>520679</v>
       </c>
       <c r="R29" t="n">
-        <v>7208667</v>
+        <v>7208301</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3570,22 +3580,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3600,65 +3600,71 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102266866</t>
+          <t>https://artportalen.se/Sighting/118557081</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118557077</v>
+        <v>102266866</v>
       </c>
       <c r="B30" t="n">
-        <v>99140</v>
+        <v>102464</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>221343</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Marsliden, Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520504</v>
+        <v>520611</v>
       </c>
       <c r="R30" t="n">
-        <v>7208434</v>
+        <v>7208667</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3682,12 +3688,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3702,24 +3718,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elias Forsberg, Anna Johansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118557077</t>
+          <t>https://artportalen.se/Sighting/102266866</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118557082</v>
+        <v>118557077</v>
       </c>
       <c r="B31" t="n">
         <v>99140</v>
@@ -3754,10 +3770,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520700</v>
+        <v>520504</v>
       </c>
       <c r="R31" t="n">
-        <v>7208335</v>
+        <v>7208434</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3815,13 +3831,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118557082</t>
+          <t>https://artportalen.se/Sighting/118557077</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118557110</v>
+        <v>118557082</v>
       </c>
       <c r="B32" t="n">
         <v>99140</v>
@@ -3856,10 +3872,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520523</v>
+        <v>520700</v>
       </c>
       <c r="R32" t="n">
-        <v>7208301</v>
+        <v>7208335</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3917,13 +3933,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118557110</t>
+          <t>https://artportalen.se/Sighting/118557082</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118557118</v>
+        <v>118557110</v>
       </c>
       <c r="B33" t="n">
         <v>99140</v>
@@ -3958,10 +3974,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520537</v>
+        <v>520523</v>
       </c>
       <c r="R33" t="n">
-        <v>7208705</v>
+        <v>7208301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4018,6 +4034,108 @@
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557110</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118557118</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kallkällmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>520537</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7208705</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elias Forsberg, Anna Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118557118</t>
         </is>
@@ -4057,6 +4175,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59019-2024 artfynd.xlsx
+++ b/artfynd/A 59019-2024 artfynd.xlsx
@@ -3267,7 +3267,7 @@
         <v>136162944</v>
       </c>
       <c r="B27" t="n">
-        <v>57820</v>
+        <v>57821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 59019-2024 artfynd.xlsx
+++ b/artfynd/A 59019-2024 artfynd.xlsx
@@ -3267,7 +3267,7 @@
         <v>136162944</v>
       </c>
       <c r="B27" t="n">
-        <v>57821</v>
+        <v>57825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 59019-2024 artfynd.xlsx
+++ b/artfynd/A 59019-2024 artfynd.xlsx
@@ -3267,7 +3267,7 @@
         <v>136162944</v>
       </c>
       <c r="B27" t="n">
-        <v>57825</v>
+        <v>57826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
